--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="500">
   <si>
     <t>Filename</t>
   </si>
@@ -808,688 +808,712 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9930,0.0014,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.1268,0.0002,0.0000,0.9553</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9875,0.0014,0.0039,0.0007</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.9890,0.0001,0.0003,0.0059</t>
+  </si>
+  <si>
+    <t>0.6243,0.0003,0.0003,0.4126</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9288,0.0023,0.0428,0.0007</t>
+  </si>
+  <si>
+    <t>0.0031,0.0011,0.9974,0.0001</t>
+  </si>
+  <si>
+    <t>0.8856,0.0006,0.1767,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.9974,0.0004,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9992,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0140,0.9876,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.9981,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.7256,0.0003,0.4183,0.0000</t>
+  </si>
+  <si>
+    <t>0.2939,0.0002,0.8528,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0388,0.0015,0.9439,0.0013</t>
+  </si>
+  <si>
+    <t>0.0004,0.0003,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9995,0.0004</t>
+  </si>
+  <si>
+    <t>0.5587,0.3857,0.0033,0.0007</t>
+  </si>
+  <si>
+    <t>0.7715,0.0196,0.0981,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0031,0.9988,0.0265</t>
+  </si>
+  <si>
+    <t>0.0031,0.9811,0.0176,0.0008</t>
+  </si>
+  <si>
+    <t>0.9800,0.0169,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.9978,0.0010,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.4693,0.5761,0.0032,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.9880,0.0260,0.0009</t>
+  </si>
+  <si>
+    <t>0.0099,0.0325,0.8814,0.0108</t>
+  </si>
+  <si>
+    <t>0.0043,0.0003,0.9796,0.0088</t>
+  </si>
+  <si>
+    <t>0.0104,0.0013,0.9809,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0009,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0035,0.9909,0.0029,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0041,0.6713,0.0014,0.9313</t>
+  </si>
+  <si>
+    <t>0.0006,0.9972,0.0010,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0103,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0042,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0014,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0125,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9727,0.0072,0.0142,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9997,0.0047</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9901,0.9952,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0023,0.9974,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9708,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9893,0.0001,0.0204,0.0000</t>
+  </si>
+  <si>
+    <t>0.9048,0.0003,0.1238,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0039</t>
+  </si>
+  <si>
+    <t>0.0000,0.9093,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9946,0.9709,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.0604,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.8807,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0000,0.0011,0.9987</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0013,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.1202,0.9957</t>
+  </si>
+  <si>
+    <t>0.0010,0.0004,0.0023,0.9985</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0019,0.9719,0.3469,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.9736,0.9219,0.0001</t>
+  </si>
+  <si>
+    <t>0.0036,0.6226,0.7997,0.0013</t>
+  </si>
+  <si>
+    <t>0.0011,0.0270,0.9753,0.0029</t>
+  </si>
+  <si>
+    <t>0.0000,0.9549,0.9877,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9933,0.9493,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0011,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9954,0.0025,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0006,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0007,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9946,0.0033,0.0011,0.0003</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0002,0.0002</t>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0004,0.9990,0.0008</t>
+  </si>
+  <si>
+    <t>0.0026,0.0011,0.9951,0.0008</t>
+  </si>
+  <si>
+    <t>0.9794,0.0005,0.0047,0.0004</t>
+  </si>
+  <si>
+    <t>0.0751,0.0001,0.9627,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9987,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8989,0.1335,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.2966,0.0017,0.7152,0.0004</t>
+  </si>
+  <si>
+    <t>0.0678,0.0001,0.9608,0.0002</t>
+  </si>
+  <si>
+    <t>0.4130,0.4798,0.0047,0.0004</t>
+  </si>
+  <si>
+    <t>0.2319,0.0375,0.2999,0.0134</t>
+  </si>
+  <si>
+    <t>0.0018,0.0056,0.0044,0.9957</t>
+  </si>
+  <si>
+    <t>0.0005,0.9990,0.0028,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0014</t>
+  </si>
+  <si>
+    <t>0.0000,0.9985,0.9934,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9994,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8822,0.0534,0.0181,0.0001</t>
+  </si>
+  <si>
+    <t>0.7672,0.2178,0.0067,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0010,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.3252,0.9945,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.7496,0.9964,0.0000</t>
+  </si>
+  <si>
+    <t>0.0038,0.0064,0.9905,0.0003</t>
+  </si>
+  <si>
+    <t>0.0044,0.0054,0.9890,0.0004</t>
+  </si>
+  <si>
+    <t>0.9873,0.0003,0.0070,0.0001</t>
+  </si>
+  <si>
+    <t>0.0997,0.0002,0.9266,0.0004</t>
+  </si>
+  <si>
+    <t>0.0071,0.0002,0.9950,0.0001</t>
+  </si>
+  <si>
+    <t>0.9450,0.0006,0.0484,0.0005</t>
+  </si>
+  <si>
+    <t>0.0562,0.0000,0.0000,0.9890</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0003,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.8863,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0009,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.9931,0.0002,0.0046</t>
+  </si>
+  <si>
+    <t>0.9980,0.0004,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.1674,0.8654,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9266,0.0012,0.0022,0.0316</t>
+  </si>
+  <si>
+    <t>0.0005,0.0017,0.9986,0.0007</t>
+  </si>
+  <si>
+    <t>0.9735,0.0001,0.0024,0.0144</t>
+  </si>
+  <si>
+    <t>0.9946,0.0001,0.0031,0.0004</t>
+  </si>
+  <si>
+    <t>0.0170,0.9716,0.0048,0.0019</t>
+  </si>
+  <si>
+    <t>0.9925,0.0022,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0004,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.0901,0.7656,0.0213,0.0029</t>
+  </si>
+  <si>
+    <t>0.9699,0.0022,0.0190,0.0001</t>
+  </si>
+  <si>
+    <t>0.9788,0.0118,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9937,0.0016,0.0022,0.0005</t>
+  </si>
+  <si>
+    <t>0.9913,0.0020,0.0017,0.0017</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9916,0.0065,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.5382,0.4759,0.0076,0.0002</t>
+  </si>
+  <si>
+    <t>0.7905,0.2458,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.3394,0.0077,0.7066,0.0016</t>
+  </si>
+  <si>
+    <t>0.9960,0.0015,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9973,0.0011,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0019,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0014,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.9850,0.0053,0.0043,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0117,0.9963,0.0003</t>
+  </si>
+  <si>
+    <t>0.0027,0.0001,0.9974,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.0056,0.9977,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0014,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0060,0.0021,0.9909,0.0005</t>
+  </si>
+  <si>
+    <t>0.0033,0.0001,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.6713,0.0208,0.1350,0.0019</t>
+  </si>
+  <si>
+    <t>0.5800,0.0011,0.4817,0.0001</t>
+  </si>
+  <si>
+    <t>0.1154,0.0320,0.7073,0.0002</t>
+  </si>
+  <si>
+    <t>0.0706,0.0010,0.9396,0.0001</t>
+  </si>
+  <si>
+    <t>0.9808,0.0008,0.0124,0.0003</t>
+  </si>
+  <si>
+    <t>0.0769,0.0034,0.9187,0.0005</t>
+  </si>
+  <si>
+    <t>0.0063,0.9908,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.0024,0.9973,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.3084,0.7458,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9365,0.0903,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0156,0.9845,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9814,0.0070,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0000,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.8960,0.0159,0.0265,0.0019</t>
+  </si>
+  <si>
+    <t>0.0110,0.0025,0.9838,0.0007</t>
+  </si>
+  <si>
+    <t>0.9247,0.0022,0.0509,0.0011</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9996,0.0005</t>
+  </si>
+  <si>
+    <t>0.0016,0.0362,0.9879,0.0015</t>
+  </si>
+  <si>
+    <t>0.0037,0.0018,0.9938,0.0002</t>
+  </si>
+  <si>
+    <t>0.0051,0.0007,0.9897,0.0013</t>
+  </si>
+  <si>
+    <t>0.0012,0.0144,0.9912,0.0012</t>
+  </si>
+  <si>
+    <t>0.9982,0.0008,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9951,0.0026,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9985,0.0006,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9957,0.0031,0.0004,0.0001</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9990,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9925,0.0003,0.0042,0.0000</t>
-  </si>
-  <si>
-    <t>0.0093,0.0028,0.9908,0.0004</t>
-  </si>
-  <si>
-    <t>0.9844,0.0003,0.0156,0.0000</t>
-  </si>
-  <si>
-    <t>0.0099,0.0001,0.9943,0.0001</t>
-  </si>
-  <si>
-    <t>0.9389,0.0005,0.0542,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0615,0.9561,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.9989,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.5924,0.0003,0.5146,0.0003</t>
-  </si>
-  <si>
-    <t>0.0126,0.0006,0.9835,0.0012</t>
-  </si>
-  <si>
-    <t>0.0025,0.0001,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0107,0.0008,0.9782,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.2627,0.0001,0.8365,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0000,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.3869,0.5313,0.0064,0.0011</t>
-  </si>
-  <si>
-    <t>0.9639,0.0103,0.0121,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.0009,0.9994,0.0059</t>
-  </si>
-  <si>
-    <t>0.0008,0.9961,0.0071,0.0003</t>
-  </si>
-  <si>
-    <t>0.9870,0.0033,0.0059,0.0005</t>
-  </si>
-  <si>
-    <t>0.9626,0.0097,0.0112,0.0008</t>
-  </si>
-  <si>
-    <t>0.6847,0.3716,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.9914,0.0282,0.0002</t>
-  </si>
-  <si>
-    <t>0.0107,0.7663,0.0457,0.0129</t>
-  </si>
-  <si>
-    <t>0.0055,0.0009,0.9850,0.0065</t>
-  </si>
-  <si>
-    <t>0.0016,0.0011,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.0039,0.0001,0.9956,0.0002</t>
-  </si>
-  <si>
-    <t>0.0052,0.0070,0.9924,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9986,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0271,0.1217,0.0006,0.9293</t>
-  </si>
-  <si>
-    <t>0.0061,0.9783,0.0026,0.0042</t>
-  </si>
-  <si>
-    <t>0.0002,0.9982,0.0231,0.0013</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0023,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0192,0.9982,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.0673,0.9937,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.9982,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0048,0.0010,0.9947,0.0003</t>
-  </si>
-  <si>
-    <t>0.9915,0.0065,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9881,0.0072,0.0030,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.0015,0.9994,0.0074</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0007,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9969,0.0025,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9887,0.9353,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0005,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0162,0.9991,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9196,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9998,0.0048</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0000,0.0036,0.0000</t>
-  </si>
-  <si>
-    <t>0.0303,0.0002,0.9817,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9998,0.0021</t>
-  </si>
-  <si>
-    <t>0.0000,0.9508,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9941,0.8862,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.4796,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9965,0.9252,0.0000</t>
-  </si>
-  <si>
-    <t>0.0096,0.0001,0.0011,0.9948</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0008,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0022,0.0000,0.0017,0.9984</t>
-  </si>
-  <si>
-    <t>0.0011,0.0003,0.0013,0.9987</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.0003,0.9996</t>
-  </si>
-  <si>
-    <t>0.0002,0.9904,0.6509,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9934,0.9637,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9346,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0260,0.9968,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9893,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.7677,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0005,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9975,0.0011,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0057,0.0001,0.9971,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0006,0.9972,0.0002</t>
-  </si>
-  <si>
-    <t>0.9079,0.0012,0.0519,0.0023</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9995,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9978,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.0010,0.9977,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0410,0.9684,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.6830,0.0055,0.2708,0.0002</t>
-  </si>
-  <si>
-    <t>0.2138,0.0003,0.8615,0.0002</t>
-  </si>
-  <si>
-    <t>0.5934,0.0124,0.2298,0.0017</t>
-  </si>
-  <si>
-    <t>0.9212,0.0283,0.0061,0.0004</t>
-  </si>
-  <si>
-    <t>0.0033,0.0064,0.0087,0.9924</t>
-  </si>
-  <si>
-    <t>0.0002,0.9989,0.0136,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.9794,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9983,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9152,0.0194,0.0290,0.0001</t>
-  </si>
-  <si>
-    <t>0.5162,0.5118,0.0050,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.2632,0.9972,0.0002</t>
-  </si>
-  <si>
-    <t>0.0027,0.0703,0.9873,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0046,0.9976,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.0005,0.9980,0.0002</t>
-  </si>
-  <si>
-    <t>0.9899,0.0005,0.0036,0.0001</t>
-  </si>
-  <si>
-    <t>0.0574,0.0005,0.9572,0.0003</t>
-  </si>
-  <si>
-    <t>0.0992,0.0001,0.9378,0.0002</t>
-  </si>
-  <si>
-    <t>0.8165,0.0007,0.2140,0.0004</t>
-  </si>
-  <si>
-    <t>0.0802,0.0000,0.0000,0.9792</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.9937,0.7909,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0008,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.7280,0.3270,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.9979,0.0005,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9062,0.1292,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.2727,0.0001,0.0037,0.8233</t>
-  </si>
-  <si>
-    <t>0.0003,0.0020,0.9989,0.0039</t>
-  </si>
-  <si>
-    <t>0.9477,0.0001,0.0097,0.0112</t>
-  </si>
-  <si>
-    <t>0.9925,0.0008,0.0032,0.0010</t>
-  </si>
-  <si>
-    <t>0.0102,0.9885,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9499,0.0132,0.0162,0.0019</t>
-  </si>
-  <si>
-    <t>0.9739,0.0005,0.0223,0.0003</t>
-  </si>
-  <si>
-    <t>0.2152,0.5653,0.0228,0.0010</t>
-  </si>
-  <si>
-    <t>0.9917,0.0011,0.0040,0.0001</t>
-  </si>
-  <si>
-    <t>0.9646,0.0102,0.0086,0.0004</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9947,0.0009,0.0023,0.0006</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0008,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9902,0.0060,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.8439,0.1832,0.0027,0.0002</t>
-  </si>
-  <si>
-    <t>0.9667,0.0507,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0067,0.0017,0.9949,0.0001</t>
-  </si>
-  <si>
-    <t>0.9970,0.0018,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0007,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9845,0.0109,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.9782,0.0076,0.0074,0.0014</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.2634,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0025,0.9984,0.0009</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.0101,0.0043,0.9814,0.0012</t>
-  </si>
-  <si>
-    <t>0.7036,0.0006,0.4466,0.0000</t>
-  </si>
-  <si>
-    <t>0.0469,0.0062,0.9182,0.0011</t>
-  </si>
-  <si>
-    <t>0.0007,0.0004,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0241,0.2718,0.4308,0.0013</t>
-  </si>
-  <si>
-    <t>0.0322,0.0059,0.9535,0.0001</t>
-  </si>
-  <si>
-    <t>0.6240,0.0020,0.3110,0.0039</t>
-  </si>
-  <si>
-    <t>0.0073,0.0004,0.9940,0.0001</t>
-  </si>
-  <si>
-    <t>0.0157,0.9850,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.0629,0.9553,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.4009,0.6437,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.9921,0.0079,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0361,0.9706,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9938,0.0025,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9907,0.0002,0.0064,0.0001</t>
-  </si>
-  <si>
-    <t>0.9544,0.0171,0.0011,0.0008</t>
-  </si>
-  <si>
-    <t>0.0770,0.0038,0.8854,0.0076</t>
-  </si>
-  <si>
-    <t>0.1258,0.0067,0.8276,0.0087</t>
-  </si>
-  <si>
-    <t>0.0057,0.0008,0.9920,0.0039</t>
-  </si>
-  <si>
-    <t>0.0029,0.0151,0.9867,0.0014</t>
-  </si>
-  <si>
-    <t>0.0002,0.0024,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0019,0.0005,0.9954,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0019,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9899,0.0079,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0009,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9936,0.0043,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0009,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.0037,0.0126,0.9872,0.0032</t>
-  </si>
-  <si>
-    <t>0.9025,0.0025,0.1044,0.0025</t>
+    <t>0.9986,0.0002,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0163,0.0061,0.9681,0.0045</t>
+  </si>
+  <si>
+    <t>0.9815,0.0010,0.0128,0.0010</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0006,0.0009,0.9985,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0135,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9995,0.0001</t>
+    <t>0.0000,0.0002,0.9999,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.1276,0.9990,0.0002</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0012,0.0013,0.9966,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0015,0.9978,0.0059</t>
-  </si>
-  <si>
-    <t>0.9609,0.0012,0.0267,0.0007</t>
-  </si>
-  <si>
-    <t>0.5048,0.0000,0.6377,0.0002</t>
-  </si>
-  <si>
-    <t>0.9955,0.0001,0.0033,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0017,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0107,0.0052,0.9743,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0022,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0033,0.9977,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.0015,0.9984,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0029,0.0010,0.9940,0.0014</t>
-  </si>
-  <si>
-    <t>0.0058,0.0058,0.9866,0.0020</t>
-  </si>
-  <si>
-    <t>0.0155,0.0012,0.9716,0.0012</t>
-  </si>
-  <si>
-    <t>0.9936,0.0001,0.0003,0.0032</t>
-  </si>
-  <si>
-    <t>0.0031,0.0004,0.0000,0.9992</t>
-  </si>
-  <si>
-    <t>0.0044,0.0002,0.0001,0.9986</t>
-  </si>
-  <si>
-    <t>0.7587,0.0008,0.0005,0.1825</t>
+    <t>0.0002,0.0002,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0005,0.9967,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0012,0.9968,0.0021</t>
+  </si>
+  <si>
+    <t>0.9482,0.0037,0.0194,0.0008</t>
+  </si>
+  <si>
+    <t>0.7508,0.0000,0.4629,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9957,0.0033,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0007,0.9959,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0027,0.9985,0.0002</t>
+  </si>
+  <si>
+    <t>0.0079,0.0058,0.9812,0.0017</t>
+  </si>
+  <si>
+    <t>0.0088,0.0012,0.9878,0.0007</t>
+  </si>
+  <si>
+    <t>0.0450,0.0058,0.9164,0.0028</t>
+  </si>
+  <si>
+    <t>0.0613,0.0005,0.9335,0.0021</t>
+  </si>
+  <si>
+    <t>0.9986,0.0000,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0022,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0223,0.0003,0.0003,0.9934</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.8895,0.0009,0.0001,0.0501</t>
   </si>
 </sst>
 </file>
@@ -1875,7 +1899,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1889,7 +1913,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1903,7 +1927,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1914,10 +1938,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1931,7 +1955,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1945,7 +1969,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1959,7 +1983,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2001,7 +2025,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2015,7 +2039,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2029,7 +2053,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2043,7 +2067,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2057,7 +2081,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2071,7 +2095,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2085,7 +2109,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2099,7 +2123,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2113,7 +2137,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2127,7 +2151,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2141,7 +2165,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2155,7 +2179,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2169,7 +2193,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2180,10 +2204,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2197,7 +2221,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2211,7 +2235,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2225,7 +2249,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2239,7 +2263,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2253,7 +2277,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2267,7 +2291,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2278,10 +2302,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2295,7 +2319,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2309,7 +2333,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2323,7 +2347,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2337,7 +2361,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2351,7 +2375,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2362,10 +2386,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2379,7 +2403,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2390,10 +2414,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2407,7 +2431,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2421,7 +2445,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2435,7 +2459,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2449,7 +2473,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2463,7 +2487,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2477,7 +2501,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2488,10 +2512,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2505,7 +2529,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2519,7 +2543,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2533,7 +2557,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2547,7 +2571,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2561,7 +2585,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2575,7 +2599,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2589,7 +2613,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2603,7 +2627,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2617,7 +2641,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2631,7 +2655,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2645,7 +2669,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2659,7 +2683,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2673,7 +2697,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2687,7 +2711,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>318</v>
+        <v>271</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2701,7 +2725,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2715,7 +2739,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2729,7 +2753,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2743,7 +2767,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2757,7 +2781,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2771,7 +2795,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2785,7 +2809,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2799,7 +2823,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2813,7 +2837,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>279</v>
+        <v>328</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2827,7 +2851,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2838,10 +2862,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2855,7 +2879,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2869,7 +2893,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2883,7 +2907,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2897,7 +2921,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2911,7 +2935,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2925,7 +2949,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2939,7 +2963,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2953,7 +2977,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2967,7 +2991,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2981,7 +3005,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2995,7 +3019,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3006,10 +3030,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3023,7 +3047,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3037,7 +3061,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3051,7 +3075,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3065,7 +3089,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3079,7 +3103,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3093,7 +3117,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3107,7 +3131,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3121,7 +3145,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3135,7 +3159,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3149,7 +3173,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3163,7 +3187,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>348</v>
+        <v>270</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3177,7 +3201,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3191,7 +3215,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3205,7 +3229,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>355</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3219,7 +3243,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3233,7 +3257,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3247,7 +3271,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3261,7 +3285,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>357</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3275,7 +3299,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3289,7 +3313,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>269</v>
+        <v>355</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3303,7 +3327,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3317,7 +3341,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3331,7 +3355,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3345,7 +3369,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3359,7 +3383,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3373,7 +3397,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>359</v>
+        <v>328</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3387,7 +3411,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3401,7 +3425,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3415,7 +3439,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3429,7 +3453,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3443,7 +3467,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3454,10 +3478,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3468,10 +3492,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3485,7 +3509,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3496,10 +3520,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3510,10 +3534,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D119" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3527,7 +3551,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3541,7 +3565,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3555,7 +3579,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3569,7 +3593,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3583,7 +3607,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3597,7 +3621,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3611,7 +3635,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3622,10 +3646,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3639,7 +3663,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>273</v>
+        <v>380</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3653,7 +3677,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3667,7 +3691,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3681,7 +3705,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3695,7 +3719,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3709,7 +3733,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3723,7 +3747,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3737,7 +3761,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3751,7 +3775,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3762,10 +3786,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3779,7 +3803,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3793,7 +3817,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3807,7 +3831,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3821,7 +3845,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3835,7 +3859,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3849,7 +3873,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3863,7 +3887,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3877,7 +3901,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>335</v>
+        <v>397</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3891,7 +3915,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3905,7 +3929,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3919,7 +3943,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3933,7 +3957,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3944,10 +3968,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3961,7 +3985,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3972,10 +3996,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3989,7 +4013,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4000,10 +4024,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4017,7 +4041,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4031,7 +4055,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4045,7 +4069,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4059,7 +4083,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4073,7 +4097,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4087,7 +4111,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4101,7 +4125,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4115,7 +4139,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4129,7 +4153,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4143,7 +4167,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4157,7 +4181,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>269</v>
+        <v>416</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4171,7 +4195,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4185,7 +4209,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4199,7 +4223,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4213,7 +4237,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>411</v>
+        <v>384</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4227,7 +4251,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4241,7 +4265,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4255,7 +4279,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4269,7 +4293,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4283,7 +4307,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4297,7 +4321,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4311,7 +4335,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4325,7 +4349,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4339,7 +4363,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4353,7 +4377,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>349</v>
+        <v>428</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4367,7 +4391,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4381,7 +4405,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4395,7 +4419,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4409,7 +4433,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4423,7 +4447,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4437,7 +4461,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4451,7 +4475,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4465,7 +4489,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4479,7 +4503,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>287</v>
+        <v>437</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4493,7 +4517,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4507,7 +4531,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4518,10 +4542,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4532,10 +4556,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4546,10 +4570,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4560,10 +4584,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4577,7 +4601,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4591,7 +4615,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4605,7 +4629,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4619,7 +4643,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4633,7 +4657,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4647,7 +4671,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4661,7 +4685,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4675,7 +4699,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4689,7 +4713,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4703,7 +4727,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4717,7 +4741,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4731,7 +4755,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4742,10 +4766,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4759,7 +4783,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4773,7 +4797,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4787,7 +4811,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4801,7 +4825,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4815,7 +4839,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4829,7 +4853,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4843,7 +4867,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4857,7 +4881,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4871,7 +4895,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4885,7 +4909,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4899,7 +4923,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4913,7 +4937,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4927,7 +4951,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>460</v>
+        <v>359</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4941,7 +4965,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4955,7 +4979,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4969,7 +4993,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4983,7 +5007,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4997,7 +5021,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5011,7 +5035,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5025,7 +5049,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5039,7 +5063,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5053,7 +5077,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5067,7 +5091,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5081,7 +5105,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5095,7 +5119,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5106,10 +5130,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5123,7 +5147,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5137,7 +5161,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5151,7 +5175,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>476</v>
+        <v>351</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5165,7 +5189,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5179,7 +5203,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>354</v>
+        <v>485</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5193,7 +5217,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>348</v>
+        <v>274</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5207,7 +5231,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5221,7 +5245,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5235,7 +5259,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>413</v>
+        <v>271</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5249,7 +5273,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5263,7 +5287,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5277,7 +5301,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5291,7 +5315,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5305,7 +5329,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>484</v>
+        <v>314</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5319,7 +5343,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5333,7 +5357,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5347,7 +5371,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5361,7 +5385,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5375,7 +5399,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5389,7 +5413,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5403,7 +5427,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>335</v>
+        <v>397</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5417,7 +5441,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>335</v>
+        <v>498</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5431,7 +5455,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
